--- a/AtchisonRegime/Outputs/Canada/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Canada/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10521,7 +10521,7 @@
         <v>-1.15907664912445</v>
       </c>
       <c r="C306" t="n">
-        <v>0.09458390577924577</v>
+        <v>0.09177840895191415</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -10554,7 +10554,7 @@
         <v>-1.189286116851168</v>
       </c>
       <c r="C307" t="n">
-        <v>0.1116244582638488</v>
+        <v>0.1104426686636601</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>-1.178902114643448</v>
       </c>
       <c r="C308" t="n">
-        <v>0.1308996091349146</v>
+        <v>0.1301523842624262</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>-1.278628121662478</v>
       </c>
       <c r="C309" t="n">
-        <v>0.1527007472235339</v>
+        <v>0.1503419548343929</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>-1.374494603709673</v>
       </c>
       <c r="C310" t="n">
-        <v>0.1721220892219018</v>
+        <v>0.16800720720337</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>-1.390151577988231</v>
       </c>
       <c r="C311" t="n">
-        <v>0.1772707817448261</v>
+        <v>0.1732999046664966</v>
       </c>
       <c r="D311" t="b">
         <v>0</v>
@@ -10719,7 +10719,7 @@
         <v>-1.325191021733015</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1710330385060329</v>
+        <v>0.1587151530727753</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
@@ -10752,7 +10752,7 @@
         <v>-1.221578075441744</v>
       </c>
       <c r="C313" t="n">
-        <v>0.150486126309403</v>
+        <v>0.1273918536019111</v>
       </c>
       <c r="D313" t="b">
         <v>0</v>
@@ -10785,7 +10785,7 @@
         <v>-1.1752475478079</v>
       </c>
       <c r="C314" t="n">
-        <v>0.1191287375318849</v>
+        <v>0.08939277802379972</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -10818,7 +10818,7 @@
         <v>-1.009799539259991</v>
       </c>
       <c r="C315" t="n">
-        <v>0.07483996014503268</v>
+        <v>0.04324614692355425</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
@@ -10848,10 +10848,10 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.8349609292392597</v>
+        <v>-0.8803880031974337</v>
       </c>
       <c r="C316" t="n">
-        <v>0.05546106636326892</v>
+        <v>0.01723553256778737</v>
       </c>
       <c r="D316" t="b">
         <v>0</v>
@@ -10871,6 +10871,39 @@
         </is>
       </c>
       <c r="I316" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.762874187646539</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.01728298383277108</v>
+      </c>
+      <c r="D317" t="b">
+        <v>0</v>
+      </c>
+      <c r="E317" t="b">
+        <v>1</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="G317" t="n">
+        <v>325618.0893537902</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
         <is>
           <t>Type 1</t>
         </is>
